--- a/dataset/construct/dataset_splits/data_size/5_percent/merged/fold5.xlsx
+++ b/dataset/construct/dataset_splits/data_size/5_percent/merged/fold5.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN9"/>
+  <dimension ref="A1:AK9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,185 +446,170 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>DM</t>
+          <t>BMI</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>BMI</t>
+          <t>AFPRE</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>CABGPRE</t>
+          <t>LVEFPRE</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>AFPRE</t>
+          <t>PREDILATION</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>LVEFPRE</t>
+          <t>CT_ValScNCC</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>NTPROBNPPRE</t>
+          <t>CT_ValScRCC</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>PREDILATION</t>
+          <t>CT_ValScLCC</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>CT_ValScNCC</t>
+          <t>CT_ValvScTot</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>CT_ValScRCC</t>
+          <t>CT_AnnScNCC</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>CT_ValScLCC</t>
+          <t>CT_AnnScRCC</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>CT_ValvScTot</t>
+          <t>CT_AnnScLCC</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnScNCC</t>
+          <t>CT_AnnScTot</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnScRCC</t>
+          <t>CT_LVOTScNCC</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnScLCC</t>
+          <t>CT_LVOTScRCC</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnScTot</t>
+          <t>CT_LVOTScLCC</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>CT_LVOTScNCC</t>
+          <t>CT_LVOTScTot</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>CT_LVOTScRCC</t>
+          <t>SEX</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>CT_LVOTScLCC</t>
+          <t>CT_AnnMean</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>CT_LVOTScTot</t>
+          <t>ECC_INDEX</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>SEX</t>
+          <t>CT_Peri_Deri</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnMean</t>
+          <t>CT_Area_Deri</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>ECC_INDEX</t>
+          <t>nyha2</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>CT_Peri_Deri</t>
+          <t>nyha3</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>CT_Area_Deri</t>
+          <t>nyha4</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>nyha2</t>
+          <t>model1</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>nyha3</t>
+          <t>model2</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>nyha4</t>
+          <t>model3</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>model1</t>
+          <t>model4</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>model2</t>
+          <t>model7</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>model3</t>
+          <t>model8</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>model4</t>
+          <t>brand2</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>model7</t>
+          <t>brand8</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>model8</t>
+          <t>QRSADM</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
-        <is>
-          <t>brand2</t>
-        </is>
-      </c>
-      <c r="AL1" s="1" t="inlineStr">
-        <is>
-          <t>brand8</t>
-        </is>
-      </c>
-      <c r="AM1" s="1" t="inlineStr">
-        <is>
-          <t>QRSADM</t>
-        </is>
-      </c>
-      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>PQADM</t>
         </is>
@@ -632,7 +617,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>612</v>
+        <v>589</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -640,41 +625,43 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>82.2897330595483</v>
+        <v>78.96926572362921</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>27.7551020408163</v>
       </c>
       <c r="E2" t="n">
-        <v>31.25</v>
+        <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>60</v>
-      </c>
-      <c r="I2" t="inlineStr"/>
+        <v>114</v>
+      </c>
+      <c r="I2" t="n">
+        <v>154</v>
+      </c>
       <c r="J2" t="n">
-        <v>1</v>
+        <v>132</v>
       </c>
       <c r="K2" t="n">
-        <v>192</v>
+        <v>400</v>
       </c>
       <c r="L2" t="n">
-        <v>39.8</v>
+        <v>10</v>
       </c>
       <c r="M2" t="n">
-        <v>32.1</v>
+        <v>21</v>
       </c>
       <c r="N2" t="n">
-        <v>263.9</v>
+        <v>11</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
@@ -683,34 +670,34 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>21.3</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>0.34</v>
       </c>
       <c r="W2" t="n">
-        <v>2</v>
+        <v>23.2365673542144</v>
       </c>
       <c r="X2" t="n">
-        <v>22.65</v>
+        <v>21.4357677787856</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.173387096774194</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>22.5362872421696</v>
+        <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>22.0244421422418</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="n">
         <v>0</v>
@@ -725,36 +712,27 @@
         <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG2" t="n">
         <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>122</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>160</v>
+        <v>180</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>959</v>
+        <v>936</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -762,79 +740,79 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>75.6452314814815</v>
+        <v>91.0289564795802</v>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>23.1111111111111</v>
       </c>
       <c r="E3" t="n">
-        <v>19.9510204081632</v>
+        <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G3" t="n">
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>60</v>
+        <v>396</v>
       </c>
       <c r="I3" t="n">
-        <v>5050</v>
+        <v>148</v>
       </c>
       <c r="J3" t="n">
-        <v>1</v>
+        <v>307</v>
       </c>
       <c r="K3" t="n">
-        <v>281</v>
+        <v>851</v>
       </c>
       <c r="L3" t="n">
-        <v>78</v>
+        <v>23</v>
       </c>
       <c r="M3" t="n">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="N3" t="n">
-        <v>394</v>
+        <v>66</v>
       </c>
       <c r="O3" t="n">
-        <v>10</v>
+        <v>112</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>20.05</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>0.21</v>
       </c>
       <c r="W3" t="n">
-        <v>2</v>
+        <v>20.3717850776674</v>
       </c>
       <c r="X3" t="n">
-        <v>22.4</v>
+        <v>19.8319163664306</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.283524904214559</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>23.2365673542144</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>22.6203056614775</v>
+        <v>1</v>
       </c>
       <c r="AB3" t="n">
         <v>0</v>
@@ -849,7 +827,7 @@
         <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
         <v>0</v>
@@ -861,22 +839,15 @@
         <v>0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>118</v>
       </c>
       <c r="AK3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>126</v>
-      </c>
-      <c r="AN3" t="inlineStr"/>
+        <v>178</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>52759086</v>
+        <v>55575206</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -884,117 +855,102 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>70.8692676249144</v>
-      </c>
-      <c r="D4" t="inlineStr"/>
+        <v>79.17043121149899</v>
+      </c>
+      <c r="D4" t="n">
+        <v>15.9499054820416</v>
+      </c>
       <c r="E4" t="n">
-        <v>26.7949380165289</v>
-      </c>
-      <c r="F4" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>50</v>
+      </c>
       <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="n">
-        <v>55</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="n">
-        <v>1</v>
-      </c>
-      <c r="K4" t="n">
-        <v>130</v>
-      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="n">
-        <v>135</v>
+        <v>1119.2163</v>
       </c>
       <c r="M4" t="n">
-        <v>117</v>
+        <v>592.36646</v>
       </c>
       <c r="N4" t="n">
-        <v>382</v>
+        <v>1049.4034</v>
       </c>
       <c r="O4" t="n">
-        <v>130</v>
+        <v>2760.98616</v>
       </c>
       <c r="P4" t="n">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="Q4" t="n">
-        <v>117</v>
+        <v>37</v>
       </c>
       <c r="R4" t="n">
-        <v>334</v>
+        <v>169</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>304</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>27.526455</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>0.31</v>
       </c>
       <c r="W4" t="n">
-        <v>1</v>
+        <v>31.93326285804946</v>
       </c>
       <c r="X4" t="n">
-        <v>25</v>
+        <v>28.87135487470849</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.18</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>79</v>
+        <v>1</v>
       </c>
       <c r="AA4" t="n">
-        <v>479</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
         <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
         <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF4" t="n">
         <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
       </c>
-      <c r="AJ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>206</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>170</v>
-      </c>
+      <c r="AJ4" t="inlineStr"/>
+      <c r="AK4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>51401128</v>
+        <v>53719519</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -1002,86 +958,80 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>87.586584531143</v>
+        <v>90.3846680355921</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>22.4996371026274</v>
       </c>
       <c r="E5" t="n">
-        <v>24.8109640831758</v>
+        <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>54</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>621</v>
-      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="n">
-        <v>456</v>
+        <v>715.8074</v>
       </c>
       <c r="M5" t="n">
-        <v>439</v>
+        <v>587.9471</v>
       </c>
       <c r="N5" t="n">
-        <v>1516</v>
+        <v>313.37814</v>
       </c>
       <c r="O5" t="n">
-        <v>554</v>
+        <v>1617.13264</v>
       </c>
       <c r="P5" t="n">
-        <v>243</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>395</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1191</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>25.97578</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W5" t="n">
-        <v>1</v>
+        <v>25.93341307534075</v>
       </c>
       <c r="X5" t="n">
-        <v>29.3</v>
+        <v>25.40039953598062</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.21</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>94</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>659.3</v>
+        <v>1</v>
       </c>
       <c r="AB5" t="n">
         <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
@@ -1099,20 +1049,15 @@
         <v>0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>196</v>
       </c>
       <c r="AK5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM5" t="inlineStr"/>
-      <c r="AN5" t="inlineStr"/>
+        <v>264</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>52530138</v>
+        <v>52799807</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -1120,79 +1065,85 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>77.6618754277892</v>
-      </c>
-      <c r="D6" t="inlineStr"/>
+        <v>88.18069815195069</v>
+      </c>
+      <c r="D6" t="n">
+        <v>27.734375</v>
+      </c>
       <c r="E6" t="n">
-        <v>23.4375</v>
-      </c>
-      <c r="F6" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>48</v>
+      </c>
       <c r="G6" t="n">
         <v>1</v>
       </c>
       <c r="H6" t="n">
-        <v>55</v>
-      </c>
-      <c r="I6" t="inlineStr"/>
+        <v>244</v>
+      </c>
+      <c r="I6" t="n">
+        <v>206</v>
+      </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>259</v>
       </c>
       <c r="K6" t="n">
-        <v>105</v>
+        <v>709</v>
       </c>
       <c r="L6" t="n">
-        <v>354</v>
+        <v>227</v>
       </c>
       <c r="M6" t="n">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="N6" t="n">
-        <v>505</v>
+        <v>38</v>
       </c>
       <c r="O6" t="n">
-        <v>17</v>
+        <v>330</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>476</v>
       </c>
       <c r="Q6" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>476</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W6" t="n">
-        <v>2</v>
+        <v>25.30563595161136</v>
       </c>
       <c r="X6" t="n">
-        <v>23.9</v>
+        <v>25.15804797053717</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.19</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>74.09999999999999</v>
+        <v>1</v>
       </c>
       <c r="AA6" t="n">
-        <v>416</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
         <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
         <v>0</v>
@@ -1201,10 +1152,10 @@
         <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
         <v>0</v>
@@ -1213,24 +1164,15 @@
         <v>0</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>199</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>184</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>137</v>
+        <v>203</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>52959587</v>
+        <v>52839474</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -1238,83 +1180,85 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>84.79397672826831</v>
+        <v>87.41957563312801</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>21.1932065611845</v>
       </c>
       <c r="E7" t="n">
-        <v>26.4235698242833</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>45</v>
-      </c>
-      <c r="I7" t="inlineStr"/>
+        <v>43</v>
+      </c>
+      <c r="I7" t="n">
+        <v>43</v>
+      </c>
       <c r="J7" t="n">
-        <v>1</v>
+        <v>33</v>
       </c>
       <c r="K7" t="n">
-        <v>226</v>
+        <v>119</v>
       </c>
       <c r="L7" t="n">
-        <v>191</v>
+        <v>43</v>
       </c>
       <c r="M7" t="n">
-        <v>169</v>
+        <v>30</v>
       </c>
       <c r="N7" t="n">
-        <v>586</v>
+        <v>33</v>
       </c>
       <c r="O7" t="n">
-        <v>226</v>
+        <v>106</v>
       </c>
       <c r="P7" t="n">
-        <v>191</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>169</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>586</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U7" t="n">
-        <v>179</v>
+        <v>24.9</v>
       </c>
       <c r="V7" t="n">
-        <v>211</v>
+        <v>0.17</v>
       </c>
       <c r="W7" t="n">
-        <v>1</v>
+        <v>25.0828190312827</v>
       </c>
       <c r="X7" t="n">
-        <v>29.8</v>
+        <v>24.15627627247472</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>98</v>
+        <v>1</v>
       </c>
       <c r="AA7" t="n">
-        <v>691</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
         <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
         <v>0</v>
@@ -1323,32 +1267,27 @@
         <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG7" t="n">
         <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>195</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM7" t="inlineStr"/>
-      <c r="AN7" t="inlineStr"/>
+        <v>138</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>52964246</v>
+        <v>51967225</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -1356,75 +1295,77 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>89.4592744695414</v>
+        <v>77.75222450376459</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>28.8044139721693</v>
       </c>
       <c r="E8" t="n">
-        <v>34.5167652859961</v>
+        <v>1</v>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8" t="n">
-        <v>67</v>
-      </c>
-      <c r="I8" t="inlineStr"/>
+        <v>207</v>
+      </c>
+      <c r="I8" t="n">
+        <v>123</v>
+      </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>142</v>
       </c>
       <c r="K8" t="n">
-        <v>361</v>
+        <v>472</v>
       </c>
       <c r="L8" t="n">
-        <v>519</v>
+        <v>204</v>
       </c>
       <c r="M8" t="n">
-        <v>139</v>
+        <v>20</v>
       </c>
       <c r="N8" t="n">
-        <v>1019</v>
+        <v>124</v>
       </c>
       <c r="O8" t="n">
-        <v>281</v>
+        <v>348</v>
       </c>
       <c r="P8" t="n">
-        <v>306</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>123</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>710</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>228</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U8" t="n">
-        <v>64</v>
+        <v>23.8</v>
       </c>
       <c r="V8" t="n">
-        <v>291</v>
+        <v>0.23</v>
       </c>
       <c r="W8" t="n">
-        <v>2</v>
+        <v>24.82817112233567</v>
       </c>
       <c r="X8" t="n">
-        <v>27</v>
+        <v>23.80050994102172</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>85</v>
+        <v>1</v>
       </c>
       <c r="AA8" t="n">
-        <v>532.8</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
         <v>0</v>
@@ -1450,25 +1391,12 @@
       <c r="AI8" t="n">
         <v>0</v>
       </c>
-      <c r="AJ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>167</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>222</v>
-      </c>
+      <c r="AJ8" t="inlineStr"/>
+      <c r="AK8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>54585763</v>
+        <v>51774855</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -1476,65 +1404,79 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>71.4633812457221</v>
-      </c>
-      <c r="D9" t="inlineStr"/>
+        <v>92.62696783025319</v>
+      </c>
+      <c r="D9" t="n">
+        <v>23.4375</v>
+      </c>
       <c r="E9" t="n">
-        <v>24.8356464572681</v>
-      </c>
-      <c r="F9" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="F9" t="n">
+        <v>55</v>
+      </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H9" t="n">
-        <v>45</v>
-      </c>
-      <c r="I9" t="inlineStr"/>
+        <v>184</v>
+      </c>
+      <c r="I9" t="n">
+        <v>305</v>
+      </c>
       <c r="J9" t="n">
-        <v>1</v>
-      </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+        <v>348</v>
+      </c>
+      <c r="K9" t="n">
+        <v>837</v>
+      </c>
+      <c r="L9" t="n">
+        <v>184</v>
+      </c>
+      <c r="M9" t="n">
+        <v>305</v>
+      </c>
+      <c r="N9" t="n">
+        <v>348</v>
+      </c>
       <c r="O9" t="n">
-        <v>343</v>
+        <v>837</v>
       </c>
       <c r="P9" t="n">
-        <v>739</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>892</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1974</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>22.3</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>0.26</v>
       </c>
       <c r="W9" t="n">
-        <v>1</v>
+        <v>24.57352321338864</v>
       </c>
       <c r="X9" t="n">
-        <v>24.1</v>
+        <v>23.32226261559675</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>77.59999999999999</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>464.9</v>
+        <v>1</v>
       </c>
       <c r="AB9" t="n">
         <v>0</v>
@@ -1552,29 +1494,16 @@
         <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
       </c>
-      <c r="AJ9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>197</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>112</v>
-      </c>
+      <c r="AJ9" t="inlineStr"/>
+      <c r="AK9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
